--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C269"/>
+  <dimension ref="A1:C282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4456,14 +4456,217 @@
           <t>Streetwise</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
+      <c r="B269" t="n">
+        <v>1984</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/streetwise/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Taylor Swift | The Eras Tour | The Final Show</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/taylor-swift-the-eras-tour-the-final-show/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>The End of an Era</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/the-end-of-an-era-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Sufjan Stevens: Carrie &amp; Lowell Live</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/sufjan-stevens-carrie-lowell-live-2017/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Cabaret</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/cabaret-1993/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Michael Jackson's Thriller</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1983</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/michael-jacksons-thriller/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Farewell My Concubine</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>1993</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/farewell-my-concubine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Cosmos</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/cosmos-2014/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>j-hope Tour 'HOPE ON THE STAGE' in JAPAN: LIVE VIEWING</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/j-hope-tour-hope-on-the-stage-in-japan-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>No me quiero ir de aquí: Una más</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/no-me-quiero-ir-de-aqui-una-mas-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Fiona Apple: MTV Live in New York, 1999</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/fiona-apple-mtv-live-in-new-york-1999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>The Voice of Hind Rajab</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/the-voice-of-hind-rajab/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Attack on Titan: Crimson Bow and Arrow</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/attack-on-titan-crimson-bow-and-arrow/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Twenty One Pilots: MTV Unplugged</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/twenty-one-pilots-mtv-unplugged/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C282"/>
+  <dimension ref="A1:C284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4591,10 +4591,8 @@
           <t>No me quiero ir de aquí: Una más</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="B278" t="n">
+        <v>2025</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -4608,10 +4606,8 @@
           <t>Fiona Apple: MTV Live in New York, 1999</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
+      <c r="B279" t="n">
+        <v>1999</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -4625,10 +4621,8 @@
           <t>The Voice of Hind Rajab</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="B280" t="n">
+        <v>2025</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -4642,10 +4636,8 @@
           <t>Attack on Titan: Crimson Bow and Arrow</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="B281" t="n">
+        <v>2014</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -4659,14 +4651,46 @@
           <t>Twenty One Pilots: MTV Unplugged</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="B282" t="n">
+        <v>2022</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/twenty-one-pilots-mtv-unplugged/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Twenty One Pilots: More Than We Ever Imagined</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/twenty-one-pilots-more-than-we-ever-imagined/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Red Hot Chili Peppers: Live at Slane Castle</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/red-hot-chili-peppers-live-at-slane-castle-2003/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C284"/>
+  <dimension ref="A1:C285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4666,10 +4666,8 @@
           <t>Twenty One Pilots: More Than We Ever Imagined</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B283" t="n">
+        <v>2026</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -4683,14 +4681,29 @@
           <t>Red Hot Chili Peppers: Live at Slane Castle</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
+      <c r="B284" t="n">
+        <v>2003</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/red-hot-chili-peppers-live-at-slane-castle-2003/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>The Phantom of the Opera at the Royal Albert Hall</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/the-phantom-of-the-opera-at-the-royal-albert-hall/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4696,14 +4696,29 @@
           <t>The Phantom of the Opera at the Royal Albert Hall</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="B285" t="n">
+        <v>2011</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/the-phantom-of-the-opera-at-the-royal-albert-hall/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Harry Styles. One Night in Manchester.</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/harry-styles-one-night-in-manchester/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4711,14 +4711,29 @@
           <t>Harry Styles. One Night in Manchester.</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
+      <c r="B286" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/harry-styles-one-night-in-manchester/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Project Hail Mary</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/harry-styles-one-night-in-manchester/</t>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/project-hail-mary/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C287"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4726,14 +4726,46 @@
           <t>Project Hail Mary</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
+      <c r="B287" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/project-hail-mary/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>JoJo's Bizarre Adventure: Steel Ball Run</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/project-hail-mary/</t>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/steel-ball-run-jojos-bizarre-adventure-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Making True Detective</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/making-true-detective/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C289"/>
+  <dimension ref="A1:C292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4741,10 +4741,8 @@
           <t>JoJo's Bizarre Adventure: Steel Ball Run</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B288" t="n">
+        <v>2026</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -4758,14 +4756,63 @@
           <t>Making True Detective</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="B289" t="n">
+        <v>2013</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/making-true-detective/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Bring Me the Horizon: L.I.V.E. in São Paulo</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bring-me-the-horizon-live-in-sao-paulo-live/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>BTS THE COMEBACK LIVE | ARIRANG</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-the-comeback-live-arirang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SUGA | Agust D TOUR “D-DAY” in JAPAN: LIVE VIEWING</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/suga-agust-d-tour-d-day-in-japan-live-viewing/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C292"/>
+  <dimension ref="A1:C297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4771,10 +4771,8 @@
           <t>Bring Me the Horizon: L.I.V.E. in São Paulo</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B290" t="n">
+        <v>2026</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -4788,10 +4786,8 @@
           <t>BTS THE COMEBACK LIVE | ARIRANG</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B291" t="n">
+        <v>2026</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -4805,14 +4801,97 @@
           <t>SUGA | Agust D TOUR “D-DAY” in JAPAN: LIVE VIEWING</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="B292" t="n">
+        <v>2023</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/suga-agust-d-tour-d-day-in-japan-live-viewing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Bring Me the Horizon: L.I.V.E. in São Paulo</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bring-me-the-horizon-live-in-sao-paulo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>BTS 2019 WORLD TOUR 'LOVE YOURSELF: SPEAK YOURSELF' LONDON Remastered</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-2019-world-tour-love-yourself-speak-yourself/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>BTS World Tour ‘Arirang’ in Goyang: Live Viewing</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-world-tour-arirang-in-goyang-live-viewing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Harry Styles - One Night Only in New York</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/harry-styles-one-night-only-in-new-york/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>War and Peace</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/war-and-peace-1965/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C297"/>
+  <dimension ref="A1:C298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4816,10 +4816,8 @@
           <t>Bring Me the Horizon: L.I.V.E. in São Paulo</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B293" t="n">
+        <v>2026</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -4833,10 +4831,8 @@
           <t>BTS 2019 WORLD TOUR 'LOVE YOURSELF: SPEAK YOURSELF' LONDON Remastered</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="B294" t="n">
+        <v>2025</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -4850,10 +4846,8 @@
           <t>BTS World Tour ‘Arirang’ in Goyang: Live Viewing</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B295" t="n">
+        <v>2026</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -4867,10 +4861,8 @@
           <t>Harry Styles - One Night Only in New York</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="B296" t="n">
+        <v>2022</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -4884,14 +4876,29 @@
           <t>War and Peace</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
+      <c r="B297" t="n">
+        <v>1965</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
           <t>https://letterboxd.com/film/war-and-peace-1965/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>JoJo's Bizarre Adventure: Diamond is Unbreakable</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/jojos-bizarre-adventure-diamond-is-unbreakable/</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D302"/>
+  <dimension ref="A1:D304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6024,10 +6024,8 @@
           <t>Apple Music Live: Lady Gaga MAYHEM Requiem</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B301" t="n">
+        <v>2026</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -6046,10 +6044,8 @@
           <t>Michael Jackson: Live at Wembley July 16, 1988</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="B302" t="n">
+        <v>2012</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -6059,6 +6055,46 @@
       <c r="D302" t="inlineStr">
         <is>
           <t>118403</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Sassy the Sasquatch</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/sassy-the-sasquatch-2022/</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>HOMECOMING: A film by Beyoncé</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/homecoming-a-film-by-beyonce/</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>593691</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D304"/>
+  <dimension ref="A1:D305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6064,10 +6064,8 @@
           <t>Sassy the Sasquatch</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="B303" t="n">
+        <v>2022</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -6082,10 +6080,8 @@
           <t>HOMECOMING: A film by Beyoncé</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="B304" t="n">
+        <v>2019</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -6095,6 +6091,28 @@
       <c r="D304" t="inlineStr">
         <is>
           <t>593691</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Interview with the Vampire</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/interview-with-the-vampire-2022/</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>921618</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D305"/>
+  <dimension ref="A1:D308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6100,10 +6100,8 @@
           <t>Interview with the Vampire</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="B305" t="n">
+        <v>2022</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -6113,6 +6111,72 @@
       <c r="D305" t="inlineStr">
         <is>
           <t>921618</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>BTS World Tour ‘Arirang’ in Busan: Live Viewing</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-world-tour-arirang-in-busan-live-viewing/</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>1701849</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>JoJo's Bizarre Adventure: Golden Wind</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/jojos-bizarre-adventure-golden-wind/</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>1377465</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Sopranos Unauthorized: Shooting Sites Uncovered</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/sopranos-unauthorized-shooting-sites-uncovered/</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>814755</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D308"/>
+  <dimension ref="A1:D311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6120,10 +6120,8 @@
           <t>BTS World Tour ‘Arirang’ in Busan: Live Viewing</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B306" t="n">
+        <v>2026</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -6142,10 +6140,8 @@
           <t>JoJo's Bizarre Adventure: Golden Wind</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="B307" t="n">
+        <v>2018</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -6164,10 +6160,8 @@
           <t>Sopranos Unauthorized: Shooting Sites Uncovered</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
+      <c r="B308" t="n">
+        <v>2002</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -6177,6 +6171,64 @@
       <c r="D308" t="inlineStr">
         <is>
           <t>814755</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Banana Fish</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/banana-fish/</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Ticket to Heaven</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/ticket-to-heaven-2026/</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Swing Girls</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/swing-girls/</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>36592</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D311"/>
+  <dimension ref="A1:D313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6180,10 +6180,8 @@
           <t>Banana Fish</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
+      <c r="B309" t="n">
+        <v>2018</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -6198,10 +6196,8 @@
           <t>Ticket to Heaven</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="B310" t="n">
+        <v>2026</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -6216,10 +6212,8 @@
           <t>Swing Girls</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
+      <c r="B311" t="n">
+        <v>2004</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -6229,6 +6223,50 @@
       <c r="D311" t="inlineStr">
         <is>
           <t>36592</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Gravity Falls: Between the Pines</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/gravity-falls-between-the-pines/</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>1602449</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SUGA | Agust D TOUR 'D-DAY' THE MOVIE</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/suga-agust-d-tour-d-day-the-movie/</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>1254724</t>
         </is>
       </c>
     </row>

--- a/top_250_data.xlsx
+++ b/top_250_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D313"/>
+  <dimension ref="A1:D323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6232,10 +6232,8 @@
           <t>Gravity Falls: Between the Pines</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+      <c r="B312" t="n">
+        <v>2016</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -6254,10 +6252,8 @@
           <t>SUGA | Agust D TOUR 'D-DAY' THE MOVIE</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+      <c r="B313" t="n">
+        <v>2024</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -6267,6 +6263,210 @@
       <c r="D313" t="inlineStr">
         <is>
           <t>1254724</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Hadestown: The Musical</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/hadestown-the-musical/</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1439808</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>The Odyssey</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/the-odyssey-2026/</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1368337</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Puella Magi Madoka Magica</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/puella-magi-madoka-magica/</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>War and Peace</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>1968</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/war-and-peace-1968/</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>29266</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>BTS WORLD TOUR [ARIRANG] in Busan</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-world-tour-arirang-in-busan/</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1701849</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>j-hope TOUR [HOPE ON THE STAGE] in Japan</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/j-hope-tour-hope-on-the-stage-in-japan/</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>1468891</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>BTS WORLD TOUR [LOVE YOURSELF : SPEAK YOURSELF] in London Remastered</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-world-tour-love-yourself-speak-yourself-2025/</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>1538062</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>BTS WORLD TOUR [ARIRANG] in Goyang</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-world-tour-arirang-in-goyang/</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>1640663</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>BTS: Permission to Dance on Stage - Seoul</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/bts-permission-to-dance-on-stage-seoul/</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>939984</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>War and Peace</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://letterboxd.com/film/war-and-peace-1967/</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>29266</t>
         </is>
       </c>
     </row>
